--- a/releaf-six-minds-en.xlsx
+++ b/releaf-six-minds-en.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phenotype: germination, root, weight</t>
+          <t xml:space="preserve">Germination, root, weight</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Brophy · must pass the membrane</t>
+          <t xml:space="preserve">Brophy · must pass the membrane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compared against proline, trehalose, ectoine</t>
+          <t xml:space="preserve">Against proline and ectoine</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Codon optimisation, shared with M3</t>
+          <t xml:space="preserve">Codon optimisation, shared</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dr. Brophy · light in, containment first</t>
+          <t xml:space="preserve">Brophy · light in, contain first</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">pNW33N-L2 (sfGFP) shuttle vector</t>
+          <t xml:space="preserve">pNW33N-L2 shuttle vector</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fold change: 535 against 670 nm</t>
+          <t xml:space="preserve">Fold change 535 / 670 nm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Characterise each promoter alone</t>
+          <t xml:space="preserve">Each promoter alone first</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cello logic and where you overrode it</t>
+          <t xml:space="preserve">Cello, and your overrides</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotech Expo · aeration and modularity</t>
+          <t xml:space="preserve">Expo · aeration, modularity</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containment: no colonies outside</t>
+          <t xml:space="preserve">No colonies outside</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passage: His-tag detected outside</t>
+          <t xml:space="preserve">His-tag detected outside</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foaming and resting-cell operation</t>
+          <t xml:space="preserve">Foaming, resting cells</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve pressure across the membrane</t>
+          <t xml:space="preserve">Valve pressure across membrane</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Reynolds number and flow regime</t>
+          <t xml:space="preserve">Reynolds and flow regime</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mass transfer, heat, oxygen at scale</t>
+          <t xml:space="preserve">Mass transfer at scale</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control stack: Arduino, pump, sensors</t>
+          <t xml:space="preserve">Arduino, pump, sensors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three independent containment layers</t>
+          <t xml:space="preserve">Three containment layers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Membrane wear and service schedule</t>
+          <t xml:space="preserve">Membrane wear, servicing</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Build files: BOM, firmware, enclosure</t>
+          <t xml:space="preserve">BOM, firmware, enclosure</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">What the team built against bought</t>
+          <t xml:space="preserve">Built against bought</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Version milestones and enclosure</t>
+          <t xml:space="preserve">Version milestones</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t xml:space="preserve">World Veg · sustainable, not organic</t>
+          <t xml:space="preserve">World Veg · not organic</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">The numbers behind the problem</t>
+          <t xml:space="preserve">The problem in numbers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tests the biostimulant path requires</t>
+          <t xml:space="preserve">Biostimulant path tests</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">The biopesticide battery avoided</t>
+          <t xml:space="preserve">Biopesticide tests avoided</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containment evidence for a regulator</t>
+          <t xml:space="preserve">Evidence a regulator accepts</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farm size against climate volatility</t>
+          <t xml:space="preserve">Farm size × volatility</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interpolation method and uncertainty</t>
+          <t xml:space="preserve">Interpolation, uncertainty</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fertilizer Act against Pesticide Act</t>
+          <t xml:space="preserve">Fertilizer vs Pesticide Act</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5065,7 +5065,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 days against several years</t>
+          <t xml:space="preserve">30 days vs years</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contained use against release</t>
+          <t xml:space="preserve">Contained use vs release</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attribution: students against collaborators</t>
+          <t xml:space="preserve">Attribution split</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yield per cartridge run</t>
+          <t xml:space="preserve">Yield per cartridge</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartridge lifetime under load</t>
+          <t xml:space="preserve">Cartridge lifetime</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Map to addressable market</t>
+          <t xml:space="preserve">Addressable market</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device cheap, cartridge recurring</t>
+          <t xml:space="preserve">Device and cartridge split</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Market sequence and its reasons</t>
+          <t xml:space="preserve">Market sequence</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patent against trade secret</t>
+          <t xml:space="preserve">Patent vs trade secret</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartridge against seasonal fungicide</t>
+          <t xml:space="preserve">Cartridge vs fungicide</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value per device per season</t>
+          <t xml:space="preserve">Value per device-season</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cost of goods per cartridge</t>
+          <t xml:space="preserve">Cost per cartridge</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gross margin and the price floor</t>
+          <t xml:space="preserve">Margin and price floor</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modular cassette as a platform</t>
+          <t xml:space="preserve">Cassette as a platform</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freedom to operate on the parts</t>
+          <t xml:space="preserve">Freedom to operate</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funding stages and their evidence</t>
+          <t xml:space="preserve">Funding stages</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competitors and the gap we sit in</t>
+          <t xml:space="preserve">Competitors and the gap</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">

--- a/releaf-six-minds-en.xlsx
+++ b/releaf-six-minds-en.xlsx
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -4783,27 +4783,27 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biostimulant path tests</t>
+          <t xml:space="preserve">Whitelist compliance</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">A fertiliser specification report from a designated testing unit, plus the abiotic-stress efficacy data supporting the declared effect. Notably, no animal toxicology and no multi-season field trials.</t>
+          <t xml:space="preserve">High school teams work inside the iGEM Whitelist: no BSL-2 organisms, no animals, no human samples, no sporulating fungi. Every strain, part and assay the other minds propose has to clear that line before it is scheduled, which is why B. subtilis 168 and Arabidopsis were never really open questions.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2.1</t>
+          <t xml:space="preserve">iGEM Whitelist</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you claim it does</t>
+          <t xml:space="preserve">Containment evidence</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P5 HP3 P2</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -4830,27 +4830,27 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biopesticide tests avoided</t>
+          <t xml:space="preserve">Safety form and risk register</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">GLP acute toxicity by oral, dermal and respiratory route; eye and skin irritation; aquatic organism and non-target insect testing; and official multi-season efficacy and phytotoxicity field trials. Years and heavy capital, avoided by not claiming disease control.</t>
+          <t xml:space="preserve">The submitted Project Safety Form and the risk register behind it: membrane permeability, phytotoxicity, AND-gate reliability, containment failure at each of the three layers. Judges can read the reviewed form on the team dashboard, so it has to agree with what the panel says out loud.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2.1</t>
+          <t xml:space="preserve">Safety form × §6.1</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you claim it does</t>
+          <t xml:space="preserve">Containment evidence</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P5 HP3 P8</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -4877,27 +4877,27 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Evidence a regulator accepts</t>
+          <t xml:space="preserve">Biostimulant path tests</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">What a regulator needs before accepting contained use, which is a higher and different bar from what satisfies a judge in a twenty-minute session.</t>
+          <t xml:space="preserve">A fertiliser specification report from a designated testing unit, plus the abiotic-stress efficacy data supporting the declared effect. Notably, no animal toxicology and no multi-season field trials.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2</t>
+          <t xml:space="preserve">Business plan §6.2.1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containment evidence</t>
+          <t xml:space="preserve">What you claim it does</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -4914,37 +4914,37 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Farm size × volatility</t>
+          <t xml:space="preserve">Biopesticide tests avoided</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parcel-level farm-size data overlaid on an interpolated climate-volatility surface built from national weather-station records, identifying where the smallest farms meet the least predictable climate.</t>
+          <t xml:space="preserve">GLP acute toxicity by oral, dermal and respiratory route; eye and skin irritation; aquatic organism and non-target insect testing; and official multi-season efficacy and phytotoxicity field trials. Years and heavy capital, avoided by not claiming disease control.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geospatial</t>
+          <t xml:space="preserve">Business plan §6.2.1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Map into numbers</t>
+          <t xml:space="preserve">What you claim it does</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 HP2 HP6 HP5</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -4961,37 +4961,37 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Interpolation, uncertainty</t>
+          <t xml:space="preserve">Evidence a regulator accepts</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">The method used, the station density behind it, and the uncertainty you are prepared to state out loud. A modelling judge will ask for all three.</t>
+          <t xml:space="preserve">What a regulator needs before accepting contained use, which is a higher and different bar from what satisfies a judge in a twenty-minute session.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geospatial</t>
+          <t xml:space="preserve">Business plan §6.2</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Map into numbers</t>
+          <t xml:space="preserve">Containment evidence</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">P8 HP2 MS2 HP5</t>
+          <t xml:space="preserve">HP3 P3</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5018,27 +5018,27 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fertilizer vs Pesticide Act</t>
+          <t xml:space="preserve">Farm size × volatility</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abiotic stress falls under the Fertilizer Management Act via the Agriculture and Food Agency. Biotic stress falls under the Pesticide Management Act via APHIA, formerly BAPHIQ. The claim decides the statute.</t>
+          <t xml:space="preserve">Parcel-level farm-size data overlaid on an interpolated climate-volatility surface built from national weather-station records, identifying where the smallest farms meet the least predictable climate.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2.1</t>
+          <t xml:space="preserve">Geospatial</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you claim it does</t>
+          <t xml:space="preserve">Map into numbers</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P1 P3 HP2 HP6 HP5</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5065,27 +5065,27 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">30 days vs years</t>
+          <t xml:space="preserve">Interpolation, uncertainty</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fertiliser registration: roughly 20 days for the specification report plus about 7 days of review, so around 30 days total. Microbial biopesticide registration takes years.</t>
+          <t xml:space="preserve">The method used, the station density behind it, and the uncertainty you are prepared to state out loud. A modelling judge will ask for all three.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2.1</t>
+          <t xml:space="preserve">Geospatial</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you claim it does</t>
+          <t xml:space="preserve">Map into numbers</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P8 HP2 MS2 HP5</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -5112,27 +5112,27 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contained use vs release</t>
+          <t xml:space="preserve">Fertilizer vs Pesticide Act</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">The engineered B. subtilis stays sealed and only non-living metabolic byproducts are discharged, which is the argument for staying outside the GM environmental-release framework. Containment must be proven to regulators, not asserted.</t>
+          <t xml:space="preserve">Abiotic stress falls under the Fertilizer Management Act via the Agriculture and Food Agency. Biotic stress falls under the Pesticide Management Act via APHIA, formerly BAPHIQ. The claim decides the statute.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2</t>
+          <t xml:space="preserve">Business plan §6.2.1</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containment evidence</t>
+          <t xml:space="preserve">What you claim it does</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3</t>
+          <t xml:space="preserve">P3 HP2 HP3</t>
         </is>
       </c>
     </row>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5159,27 +5159,27 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Attribution split</t>
+          <t xml:space="preserve">30 days vs years</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Attributions form must separate project idea, design and execution, and name what each collaborator did. Judges check whether every field including specific tasks is filled and whether it matches what the team achieved.</t>
+          <t xml:space="preserve">Fertiliser registration: roughly 20 days for the specification report plus about 7 days of review, so around 30 days total. Microbial biopesticide registration takes years.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handbook p.25</t>
+          <t xml:space="preserve">Business plan §6.2.1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">What you claim it does</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">P6 P8</t>
+          <t xml:space="preserve">P3 HP2</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5206,27 +5206,27 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standard pages, one per award</t>
+          <t xml:space="preserve">Contained use vs release</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Each medal criterion and each Special Award has a fixed wiki URL. Judges are directed there from the ballot and are not required to hunt elsewhere, and content on external sites cannot be judged at all.</t>
+          <t xml:space="preserve">The engineered B. subtilis stays sealed and only non-living metabolic byproducts are discharged, which is the argument for staying outside the GM environmental-release framework. Containment must be proven to regulators, not asserted.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handbook p.29</t>
+          <t xml:space="preserve">Business plan §6.2</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Containment evidence</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">P8 HP5</t>
+          <t xml:space="preserve">HP3 P3</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a use the law allows and the community accepts</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5253,64 +5253,64 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Written guidance from BAPHIQ</t>
+          <t xml:space="preserve">Stakeholder-to-change register</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seek written guidance before any field or greenhouse deployment, because the agency may still classify secreted compounds from engineered bacteria as requiring GMO approval. Until that is clarified, all testing stays contained and lab-based.</t>
+          <t xml:space="preserve">One table: every conversation, the design decision it changed, and the experiment that followed. 鄭梅君 moved the assay to agar, Brophy moved containment into hardware, 黃介辰 moved release ahead of the stress, Verslue changed what we secrete. Without the table these are anecdotes; with it they are integrated human practices.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.1</t>
+          <t xml:space="preserve">All stakeholder notes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Containment evidence · What you claim it does</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HP3 P3 HP2</t>
+          <t xml:space="preserve">HP1 HP2 HP5 P5</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+          <t xml:space="preserve">Human Practices &amp; Regulation</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human Practices</t>
+          <t xml:space="preserve">Dry Lab</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">陳文亮 · printer and ink</t>
+          <t xml:space="preserve">Who this design excludes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model the business on cheap hardware and expensive consumable. Identify who pays rather than who uses. B2C is difficult and needs consultation and trust. Do not compete with cheap chemical fertiliser on price, and consider starting in foreign markets before local expansion.</t>
+          <t xml:space="preserve">A sealed device on a cartridge subscription excludes farmers who cannot carry a recurring cost, and the single-button interface exists because 黃介辰 and 陳惠雯 both described ageing rural users. Name the people this does not reach and what would have to change for it to reach them.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/10 AgriTalk</t>
+          <t xml:space="preserve">黃介辰, 陳惠雯</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5320,91 +5320,91 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1</t>
+          <t xml:space="preserve">HP3 HP4 HP6 P5</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+          <t xml:space="preserve">Human Practices &amp; Regulation</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human Practices</t>
+          <t xml:space="preserve">Dry Lab</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">正瀚 · positioning and regulation</t>
+          <t xml:space="preserve">Public forum and 農漁週</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat and drought carry the greatest market need in Taiwan. Consider the legal regulations before designing the experiment, not after. Positioning against chemical pesticides, and which farms in Taiwan run field trials.</t>
+          <t xml:space="preserve">The 9/5 public forum and 9/9 農漁週, redesigned after Green Media pushed discussion time from 10 minutes to 30 and suggested inviting the people who buy imperfect produce. Two-way events rather than presentations.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/9 正瀚生技</t>
+          <t xml:space="preserve">7/7 綠媒體</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you claim it does</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1 HP2</t>
+          <t xml:space="preserve">HP4 HP5 HP6 P5</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+          <t xml:space="preserve">Human Practices &amp; Regulation</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human Practices</t>
+          <t xml:space="preserve">Dry Lab</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">源鮮 · two customer segments</t>
+          <t xml:space="preserve">Attribution split</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smallholders want stress protection for staple crops. Large companies want growth speed and protection for high-value crops such as spices and salad vegetables. One product, two propositions.</t>
+          <t xml:space="preserve">The Attributions form must separate project idea, design and execution, and name what each collaborator did. Judges check whether every field including specific tasks is filled and whether it matches what the team achieved.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/11 源鮮智慧農場</t>
+          <t xml:space="preserve">Handbook p.25</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5414,101 +5414,101 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P5 HP1 HP4</t>
+          <t xml:space="preserve">P6 P8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+          <t xml:space="preserve">Human Practices &amp; Regulation</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human Practices</t>
+          <t xml:space="preserve">Dry Lab</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotech Expo · headline metrics</t>
+          <t xml:space="preserve">Standard pages, one per award</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Competitors anchored their booths on one or two numbers, usually yield or emissions, and reviewers repeated those numbers back. Pick the one to three figures this project will be remembered by and put them everywhere, rather than describing the mechanism and hoping the number is inferred.</t>
+          <t xml:space="preserve">Each medal criterion and each Special Award has a fixed wiki URL. Judges are directed there from the ballot and are not required to hunt elsewhere, and content on external sites cannot be judged at all.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/18 南港展覽館</t>
+          <t xml:space="preserve">Handbook p.29</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 P5 HP1</t>
+          <t xml:space="preserve">P8 HP5</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">M6</t>
+          <t xml:space="preserve">M5</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+          <t xml:space="preserve">Human Practices &amp; Regulation</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">A design decision → the person who caused it and the rule that bounds it</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wet Lab</t>
+          <t xml:space="preserve">Dry Lab</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yield per cartridge</t>
+          <t xml:space="preserve">Written guidance from BAPHIQ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">How much protectant one cartridge produces across its life, in milligrams. This is the unit that gets sold, and until the number exists the price is a guess.</t>
+          <t xml:space="preserve">Seek written guidance before any field or greenhouse deployment, because the agency may still classify secreted compounds from engineered bacteria as requiring GMO approval. Until that is clarified, all testing stays contained and lab-based.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4 reactor run</t>
+          <t xml:space="preserve">Business plan §6.1</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge</t>
+          <t xml:space="preserve">Containment evidence · What you claim it does</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">P2 P3 MS4</t>
+          <t xml:space="preserve">HP3 P3 HP2</t>
         </is>
       </c>
     </row>
@@ -5525,37 +5525,37 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wet Lab</t>
+          <t xml:space="preserve">Human Practices</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartridge lifetime</t>
+          <t xml:space="preserve">陳文亮 · printer and ink</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Days of continuous operation before output falls below the useful dose. The replacement interval is the revenue clock, so this experiment sets recurring income as directly as it sets maintenance.</t>
+          <t xml:space="preserve">Model the business on cheap hardware and expensive consumable. Identify who pays rather than who uses. B2C is difficult and needs consultation and trust. Do not compete with cheap chemical fertiliser on price, and consider starting in foreign markets before local expansion.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">M4 × business plan</t>
+          <t xml:space="preserve">4/10 AgriTalk</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge · Metabolic burden</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HW3 P2</t>
+          <t xml:space="preserve">P3 P5 HP1</t>
         </is>
       </c>
     </row>
@@ -5572,37 +5572,37 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wet Lab</t>
+          <t xml:space="preserve">Human Practices</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strain shelf stability</t>
+          <t xml:space="preserve">正瀚 · positioning and regulation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Whether a cartridge survives storage and shipping at ambient temperature, and for how long. A consumable that needs cold chain has a different cost structure and a much smaller market.</t>
+          <t xml:space="preserve">Heat and drought carry the greatest market need in Taiwan. Consider the legal regulations before designing the experiment, not after. Positioning against chemical pesticides, and which farms in Taiwan run field trials.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">正瀚 × wet lab</t>
+          <t xml:space="preserve">7/9 正瀚生技</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge</t>
+          <t xml:space="preserve">What you claim it does</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P2</t>
+          <t xml:space="preserve">P3 P5 HP1 HP2</t>
         </is>
       </c>
     </row>
@@ -5619,37 +5619,37 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Human Practices</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addressable market</t>
+          <t xml:space="preserve">源鮮 · two customer segments</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn the overlap surface into countable things: hectares inside the high-overlap regions, farms under one hectare within them, and how many devices that implies at the phase-two density. This is the step that makes the geospatial work pay for itself inside the business plan.</t>
+          <t xml:space="preserve">Smallholders want stress protection for staple crops. Large companies want growth speed and protection for high-value crops such as spices and salad vegetables. One product, two propositions.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geospatial × business plan</t>
+          <t xml:space="preserve">8/11 源鮮智慧農場</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Map into numbers · Device and cartridge</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 HP2 HP6</t>
+          <t xml:space="preserve">P3 P5 HP1 HP4</t>
         </is>
       </c>
     </row>
@@ -5666,27 +5666,27 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Human Practices</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge split</t>
+          <t xml:space="preserve">Biotech Expo · headline metrics</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">The reactor's build cost sets the hardware price and the cartridge interval sets the revenue clock. Both numbers come from M4, so the business model cannot be written without the hardware team in the room.</t>
+          <t xml:space="preserve">Competitors anchored their booths on one or two numbers, usually yield or emissions, and reviewers repeated those numbers back. Pick the one to three figures this project will be remembered by and put them everywhere, rather than describing the mechanism and hoping the number is inferred.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">陳文亮 × hardware</t>
+          <t xml:space="preserve">7/18 南港展覽館</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP1 P1</t>
+          <t xml:space="preserve">P1 P3 P5 HP1</t>
         </is>
       </c>
     </row>
@@ -5713,37 +5713,37 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Market sequence</t>
+          <t xml:space="preserve">LPA dose–response curve</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Philippines first under the NCBP contained-use guidelines. Vietnam second under Decree 43/2026/ND-CP with the Mekong salinity problem. Taiwan for closed validation. EU is long horizon only under the precautionary principle.</t>
+          <t xml:space="preserve">Our own measurement of light intensity against protectant output on the light plate apparatus. Line 1 of the plan starts here: without this curve the claim that the switch is controllable is an assertion.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2</t>
+          <t xml:space="preserve">M1 × LPA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Light dose · Device and cartridge</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P1 P2 MS4 P3</t>
         </is>
       </c>
     </row>
@@ -5760,37 +5760,37 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patent vs trade secret</t>
+          <t xml:space="preserve">Plant rescue against controls</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patent the AND-gate circuit design, the CFMDI membrane design and the dual-module architecture. Keep promoter sequences and signal-peptide combinations as trade secrets. Note the tension with iGEM's open publication requirement.</t>
+          <t xml:space="preserve">The salinity rescue scored against untreated plants, medium only, unengineered strain effluent and protectant-free reactor effluent. This is the only evidence in the plan that the product changes a plant.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.2</t>
+          <t xml:space="preserve">M1 plant assay</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Controls and calibration · Device and cartridge</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP3</t>
+          <t xml:space="preserve">P1 P2 MS4 P3</t>
         </is>
       </c>
     </row>
@@ -5807,27 +5807,27 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartridge vs fungicide</t>
+          <t xml:space="preserve">Yield per cartridge</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">One season of cartridges must cost no more than a farmer's current seasonal fungicide spend. The financial model runs a sensitivity analysis at plus or minus 20 percent on cost and on price.</t>
+          <t xml:space="preserve">How much protectant one cartridge produces across its life, in milligrams. This is the unit that gets sold, and until the number exists the price is a guess.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.1</t>
+          <t xml:space="preserve">M4 reactor run</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP3</t>
+          <t xml:space="preserve">P2 P3 MS4</t>
         </is>
       </c>
     </row>
@@ -5854,37 +5854,37 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilot success metrics</t>
+          <t xml:space="preserve">Cartridge lifetime</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 to 30 percent fewer fungicide applications per season, 10 to 15 percent crop-loss reduction under climate stress, across 20 to 50 devices and 20 to 70 farmers. Name these as targets rather than results.</t>
+          <t xml:space="preserve">Days of continuous operation before output falls below the spec floor. The replacement interval is the revenue clock, so this experiment sets recurring income as directly as it sets maintenance.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §3.4</t>
+          <t xml:space="preserve">M4 × business plan</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Device and cartridge · Metabolic burden</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2 HP3</t>
+          <t xml:space="preserve">P3 HW3 P2</t>
         </is>
       </c>
     </row>
@@ -5901,27 +5901,27 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dry Lab</t>
+          <t xml:space="preserve">Wet Lab</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deployment ramp</t>
+          <t xml:space="preserve">Strain shelf stability</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 to 50 pilot units reaching 20 to 70 farmers, then 150 to 400 across cooperatives, then 500 to 1500 across two to three countries. Bundle A is hardware with cartridges; Bundle B is hardware with an API and universal media.</t>
+          <t xml:space="preserve">Whether a cartridge survives storage and shipping at ambient temperature, and for how long. A consumable that needs cold chain has a different cost structure and a much smaller market.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §3.4</t>
+          <t xml:space="preserve">正瀚 × wet lab</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P1</t>
+          <t xml:space="preserve">P3 P2</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Value per device-season</t>
+          <t xml:space="preserve">Minimum effective activity</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">The model runs from stress frequency through protectant dose to plant benefit. Multiply the benefit by the crop price and you have what one device is worth to one farmer in one season, which is the ceiling on what anyone will pay.</t>
+          <t xml:space="preserve">The model runs the plant readout backwards to the lowest enzyme activity that still produces a measurable rescue. That figure is the product specification. Line 2 of the plan is this number and nothing else.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Model × business plan</t>
+          <t xml:space="preserve">M2 model × M1 assay</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge · Map into numbers</t>
+          <t xml:space="preserve">Device and cartridge · Trigger threshold</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6005,27 +6005,27 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cost per cartridge</t>
+          <t xml:space="preserve">Spec floor to cost structure</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Media, strain production, the membrane cartridge and the fill. Set against the reactor build cost from M4, this is the pair of numbers the printer-and-ink model stands or falls on.</t>
+          <t xml:space="preserve">The floor sets the titre a run has to reach, which sets fermentation volume, media consumption and cartridge size, which set the bill of materials. Change the floor and every cost below it moves.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOM × fermentation</t>
+          <t xml:space="preserve">M2 × M4</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device and cartridge</t>
+          <t xml:space="preserve">Device and cartridge · Metabolic burden</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HW4 P6</t>
+          <t xml:space="preserve">P3 P4 HW4</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Margin and price floor</t>
+          <t xml:space="preserve">Cost per cartridge</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cartridge cost against cartridge price gives the margin; a farmer's current seasonal fungicide spend gives the ceiling. If the two do not leave a gap, the model needs a different payer rather than a different price.</t>
+          <t xml:space="preserve">Membrane, media, strain production, the cartridge shell and the fill, costed on the build we have rather than on a supplier catalogue. Line 3 starts here.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §6.1, §7.1</t>
+          <t xml:space="preserve">M4 BOM</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P1</t>
+          <t xml:space="preserve">P3 HW4 P6</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6099,27 +6099,27 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cassette as a platform</t>
+          <t xml:space="preserve">Power and running cost</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">One chassis, swappable expression cassettes. The cloning design is why a second protectant does not need a second company, and it is what Bundle B sells: hardware plus an API, with the customer culturing their own locally isolated strain.</t>
+          <t xml:space="preserve">LED array, circulation pump and controller, measured in watts and converted to kilowatt-hours per season at the duty cycle from M1. 黃介辰 said farmers care about the electricity bill, so this is a selling number rather than a footnote.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3 × business plan</t>
+          <t xml:space="preserve">M4 × 黃介辰</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">One chassis, many products</t>
+          <t xml:space="preserve">Device and cartridge</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">P1 P3 P7</t>
+          <t xml:space="preserve">P3 HW3 HP1</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6146,27 +6146,27 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freedom to operate</t>
+          <t xml:space="preserve">Replacement cycle</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">The CcaS-CcaR system, the MoClo standard and the shuttle backbone all came from somewhere. Before any filing, check what is encumbered, what is licensed for commercial use, and what is genuinely ours to claim.</t>
+          <t xml:space="preserve">Membrane life, cartridge interval and how often someone has to visit the device. Multiply by the fleet and you have consumable demand per device-year, which is the whole recurring revenue line.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">M3 × legal</t>
+          <t xml:space="preserve">M4 × business plan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">One chassis, many products · What you claim it does</t>
+          <t xml:space="preserve">Device and cartridge</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 P7 P8</t>
+          <t xml:space="preserve">P3 HW3</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6193,17 +6193,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funding stages</t>
+          <t xml:space="preserve">Margin and price floor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Three rounds with different burdens of proof: to the Jamboree on expression and secretion data, post-Jamboree on crop trials and cost feasibility, first pilot on field data and a regulatory pathway. Naming what each funder needs to see is more convincing than naming an amount.</t>
+          <t xml:space="preserve">Cartridge cost against cartridge price gives the margin. If the gap is thin the answer is a different payer, not a different price.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business plan §7.2</t>
+          <t xml:space="preserve">Business plan §6.1, §7.1</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">P3 HP2</t>
+          <t xml:space="preserve">P3 P1</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t xml:space="preserve">A working device → a product with a price, a buyer and a margin</t>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6240,25 +6240,495 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
+          <t xml:space="preserve">What Taiwan farmers spend today</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seasonal fungicide and fertiliser spend per hectare, the crop values behind it, and what CH Biotech charges for a peptide biostimulant. The ceiling on our price is somebody else's invoice, so it has to be a real figure.</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business plan §4.3, §4.4</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P1 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Value per device-season</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rescue effect from M1 multiplied by crop price gives what one device is worth to one farmer in one season. That is the ceiling on what anyone will pay, and it comes from our assay rather than from a paper.</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M1 × model</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Device and cartridge · Map into numbers</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P4 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Addressable market from the map</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hectares inside the high-overlap regions, farms under one hectare within them, and the device count that implies at phase-two density. Line 4 begins with a count, not an adjective.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 geospatial</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Map into numbers · Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantified future impact</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The map describes conditions now. Fold in the rescue data and the duty cycle and it becomes a statement with units: hectares protected, tonnes retained, spray events removed, at a stated fleet size. Very few teams can build this, which is exactly why it is worth building.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 × M1 × model</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Map into numbers · Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 HP6 P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulatory cost and timeline</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What M5's pathway research costs the venture: roughly 30 days and a fertiliser specification report against several years, GLP animal toxicology and multi-season official trials. That difference is the capital requirement and the time to first revenue.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M5 § regulation</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What you claim it does · Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ramp and market sequence</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20 to 50 pilot units, then 150 to 400 across cooperatives, then 500 to 1500 across two or three countries. Philippines first under NCBP contained-use guidance, Vietnam second, Taiwan for closed validation.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business plan §3.4, §6.2</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pilot metrics against projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Targets are 20 to 30 percent fewer fungicide applications and 10 to 15 percent less crop loss. Name them as projections now, then let the pilot replace each one with a measurement.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business plan §3.4</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2 HP3</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IP: owned and borrowed</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Patent the AND-gate circuit, the CFMDI membrane design and the dual-module architecture; hold promoter sequences and signal-peptide combinations as trade secrets. Before any filing, check what CcaS-CcaR, MoClo and the shuttle backbone carry with them.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 × legal</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One chassis, many products · What you claim it does</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 P7 P8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cassette as a platform</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One chassis, swappable expression cassettes. The cloning design is why a second protectant needs a new cassette rather than a new company, and it is what Bundle B sells: hardware plus an API, with the customer culturing their own local strain.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 × business plan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One chassis, many products</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P1 P3 P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Funding stages</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Three rounds with different burdens of proof: to the Jamboree on expression and secretion data, post-Jamboree on crop trials and cost feasibility, first pilot on field data and a regulatory pathway. Naming what each funder needs to see beats naming an amount.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business plan §7.2</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Device and cartridge</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3 HP2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M6</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business &amp; Entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Our own data → a spec floor, a unit cost, a market and an impact number</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dry Lab</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
           <t xml:space="preserve">Competitors and the gap</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chemical fungicides are cheaper and work now. Commercial biostimulants such as CH Biotech's peptides are shelf-stable and already sold. Neither adapts when a heatwave turns into an outbreak, and that gap is the only ground worth claiming.</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
+      <c r="F143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemical fungicides are cheaper and work now. Commercial biostimulants are shelf-stable and already sold. Neither adapts when a heatwave turns into an outbreak, and that gap is the only ground worth claiming.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t xml:space="preserve">Business plan §4.3</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t xml:space="preserve">Device and cartridge</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">P1 P3</t>
         </is>
@@ -6449,17 +6919,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6951,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">26</t>
         </is>
       </c>
     </row>
@@ -6552,7 +7022,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
     </row>
@@ -6579,7 +7049,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
@@ -6606,7 +7076,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">52</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
     </row>
@@ -6633,7 +7103,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
     </row>
@@ -6660,7 +7130,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
     </row>
@@ -6741,7 +7211,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
     </row>
@@ -6876,7 +7346,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
     </row>
@@ -6957,7 +7427,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
     </row>
@@ -6984,7 +7454,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
@@ -7011,7 +7481,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7508,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7535,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7562,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7589,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7616,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
     </row>
